--- a/SRC_Common/Message_File.xlsx
+++ b/SRC_Common/Message_File.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E8EE084B-CA2C-448A-8EE6-750D81036D54}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{34CD1FBD-5819-4BBD-89FE-C9B361058C93}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79285E73-3138-47E9-AB19-54B779683989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1635" yWindow="930" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CM" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>Parameter Name &amp; doesn't exist</t>
     <phoneticPr fontId="1"/>
@@ -364,37 +364,104 @@
   <si>
     <t>en-US</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>zh-TW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>發生異常；請查看螢幕截圖。</t>
+  </si>
+  <si>
+    <t>參數名稱“&amp;”不存在。</t>
+  </si>
+  <si>
+    <t>輸入值“&amp;”不存在。</t>
+  </si>
+  <si>
+    <t>請輸入參數名稱“&amp;”的值。</t>
+  </si>
+  <si>
+    <t>您的密碼即將過期；請進行更新。</t>
+  </si>
+  <si>
+    <t>請檢查參數名稱“&amp;”的輸入值。</t>
+  </si>
+  <si>
+    <t>參數“&amp;”僅允許輸入“x”。</t>
+  </si>
+  <si>
+    <t>處理已成功完成！</t>
+  </si>
+  <si>
+    <t>輸入的路徑“&amp;”不存在。</t>
+  </si>
+  <si>
+    <t>對於參數“&amp;1”，僅擴展名“&amp;2”有效。</t>
+  </si>
+  <si>
+    <t>文件“&amp;1”和“&amp;2”中的項目順序或名稱不符。</t>
+  </si>
+  <si>
+    <t>登入已中止，因為 SAP 登入介面已在執行。</t>
+  </si>
+  <si>
+    <t>未發生錯誤。</t>
+  </si>
+  <si>
+    <t>無法取得項目名稱；請手動指定。</t>
+  </si>
+  <si>
+    <t>該物件無法被取得。</t>
+  </si>
+  <si>
+    <t>無法取得項目內容；請查看螢幕截圖。</t>
+  </si>
+  <si>
+    <t>請檢查輸入檔中的以下工作表。</t>
+  </si>
+  <si>
+    <t>無法取得 [RETURN]。</t>
+  </si>
+  <si>
+    <t>要複製的工作表“&amp;”不存在。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="Yu Gothic"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -402,21 +469,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -694,27 +775,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D757E205-299B-4B27-9B40-3DC790C2CA1E}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="18.75"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="69.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="64" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.625" style="1"/>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="84.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="60" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.28515625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -724,8 +809,11 @@
       <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -735,8 +823,11 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -746,8 +837,11 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -757,8 +851,11 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -768,8 +865,11 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -779,8 +879,11 @@
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -790,8 +893,11 @@
       <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -801,8 +907,11 @@
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -812,8 +921,11 @@
       <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -823,8 +935,11 @@
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -834,19 +949,25 @@
       <c r="C12" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -856,63 +977,81 @@
       <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" s="4" customFormat="1">
-      <c r="A15" s="4" t="s">
+      <c r="D14" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" s="4" customFormat="1">
-      <c r="A16" s="4" t="s">
+      <c r="D15" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" s="4" customFormat="1">
-      <c r="A17" s="4" t="s">
+      <c r="D16" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" s="4" customFormat="1">
-      <c r="A18" s="4" t="s">
+      <c r="D17" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" s="4" customFormat="1">
-      <c r="A19" s="4" t="s">
+      <c r="D18" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>55</v>
       </c>
@@ -921,6 +1060,9 @@
       </c>
       <c r="C20" s="1" t="s">
         <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -931,6 +1073,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C827732D69AAF14BA01846CE3CC7794A" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c45483ed6e5ce5006a52541c2b9ecbfd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0bc06b84-8904-4b80-b12f-bdecd9bbb428" xmlns:ns3="5cee1336-4f95-4b7b-89f0-d6c62532513b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e37752a973e793fedbf688ee3b208e9" ns2:_="" ns3:_="">
     <xsd:import namespace="0bc06b84-8904-4b80-b12f-bdecd9bbb428"/>
@@ -1127,23 +1284,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134912C-5EC2-4FFA-81AD-07E158E8550D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3500BB0A-E874-4ABB-839E-9FC829D71AB7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1156,9 +1302,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3500BB0A-E874-4ABB-839E-9FC829D71AB7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F134912C-5EC2-4FFA-81AD-07E158E8550D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0bc06b84-8904-4b80-b12f-bdecd9bbb428"/>
+    <ds:schemaRef ds:uri="5cee1336-4f95-4b7b-89f0-d6c62532513b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>